--- a/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,57</t>
+          <t>5,66; 14,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 11,52</t>
+          <t>3,01; 11,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,21</t>
+          <t>5,07; 11,79</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,07</t>
+          <t>1,77; 9,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,95</t>
+          <t>3,69; 13,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,64</t>
+          <t>3,85; 9,77</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 16,53</t>
+          <t>2,9; 15,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 21,76</t>
+          <t>4,19; 21,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,93</t>
+          <t>4,63; 14,87</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 12,94</t>
+          <t>4,99; 12,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,45</t>
+          <t>4,67; 10,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,13</t>
+          <t>5,5; 10,24</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 24,58</t>
+          <t>9,84; 24,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 20,64</t>
+          <t>9,83; 20,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 19,91</t>
+          <t>11,49; 19,99</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 21,69</t>
+          <t>7,06; 21,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 24,6</t>
+          <t>9,16; 24,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 20,6</t>
+          <t>9,9; 20,22</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,15</t>
+          <t>7,59; 12,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,9</t>
+          <t>7,84; 11,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,11</t>
+          <t>8,25; 11,29</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9848</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18635</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5910; 15306</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4088; 16254</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12189; 28343</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4614</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11741</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1672; 9216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3528; 12634</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7328; 18580</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3781</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10148</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1504; 7963</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2677; 13688</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5357; 17209</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17766</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15764</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33530</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10873; 28102</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10199; 23104</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23992; 44674</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>18318</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23652</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41970</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11746; 29201</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15992; 33384</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32404; 56370</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11252</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20136</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4862; 14552</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6596; 17675</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>13947; 28487</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>63212</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>72948</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>136160</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>49889; 79290</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>58683; 88218</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>116017; 158647</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 14,65</t>
+          <t>5,73; 15,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 11,95</t>
+          <t>3,05; 11,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,79</t>
+          <t>4,94; 11,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,73</t>
+          <t>1,71; 9,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,22</t>
+          <t>3,88; 13,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,77</t>
+          <t>3,62; 9,89</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 15,35</t>
+          <t>2,97; 15,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 21,44</t>
+          <t>4,1; 20,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 14,87</t>
+          <t>4,52; 15,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 12,9</t>
+          <t>4,79; 12,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,58</t>
+          <t>4,71; 10,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,24</t>
+          <t>5,39; 10,17</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 24,45</t>
+          <t>10,12; 24,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 20,53</t>
+          <t>10,13; 20,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,99</t>
+          <t>11,2; 19,81</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 21,12</t>
+          <t>6,97; 21,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 24,55</t>
+          <t>9,45; 23,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 20,22</t>
+          <t>9,41; 20,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,07</t>
+          <t>7,62; 12,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,79</t>
+          <t>7,88; 11,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,29</t>
+          <t>8,21; 11,2</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5910; 15306</t>
+          <t>5988; 15916</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4088; 16254</t>
+          <t>4145; 15683</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12189; 28343</t>
+          <t>11871; 26686</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1672; 9216</t>
+          <t>1622; 9372</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3528; 12634</t>
+          <t>3707; 12422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7328; 18580</t>
+          <t>6880; 18818</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1504; 7963</t>
+          <t>1542; 8115</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2677; 13688</t>
+          <t>2621; 12779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5357; 17209</t>
+          <t>5232; 17910</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10873; 28102</t>
+          <t>10438; 27709</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10199; 23104</t>
+          <t>10284; 23131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23992; 44674</t>
+          <t>23524; 44358</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11746; 29201</t>
+          <t>12082; 29772</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15992; 33384</t>
+          <t>16465; 33317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32404; 56370</t>
+          <t>31589; 55878</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4862; 14552</t>
+          <t>4800; 14931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6596; 17675</t>
+          <t>6801; 17274</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13947; 28487</t>
+          <t>13258; 28949</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49889; 79290</t>
+          <t>50049; 79068</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58683; 88218</t>
+          <t>58941; 87344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116017; 158647</t>
+          <t>115365; 157366</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,24</t>
+          <t>3,13; 11,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 11,53</t>
+          <t>5,48; 14,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,9</t>
+          <t>3,77; 13,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,0</t>
+          <t>1,69; 9,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,89</t>
+          <t>3,57; 9,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 15,65</t>
+          <t>4,86; 23,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 20,01</t>
+          <t>2,95; 17,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,48</t>
+          <t>4,55; 15,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,72</t>
+          <t>4,62; 10,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,6</t>
+          <t>5,89; 13,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,17</t>
+          <t>5,91; 10,43</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 24,93</t>
+          <t>10,25; 21,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 20,49</t>
+          <t>9,09; 19,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 19,81</t>
+          <t>11,1; 18,76</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 21,67</t>
+          <t>8,72; 23,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 23,99</t>
+          <t>7,25; 24,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,41; 20,55</t>
+          <t>10,15; 20,6</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,03</t>
+          <t>7,95; 11,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,67</t>
+          <t>7,72; 11,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,2</t>
+          <t>8,42; 11,11</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>17359</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5988; 15916</t>
+          <t>3806; 13410</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4145; 15683</t>
+          <t>5643; 15315</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11871; 26686</t>
+          <t>11085; 24916</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11208</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1622; 9372</t>
+          <t>3446; 12171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3707; 12422</t>
+          <t>1627; 9436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6880; 18818</t>
+          <t>6713; 17735</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10440</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1542; 8115</t>
+          <t>2766; 13456</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2621; 12779</t>
+          <t>1579; 9115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5232; 17910</t>
+          <t>5030; 17602</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33530</t>
+          <t>30586</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10438; 27709</t>
+          <t>9325; 21942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10284; 23131</t>
+          <t>10523; 23586</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23524; 44358</t>
+          <t>22503; 39686</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>38139</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12082; 29772</t>
+          <t>15202; 31465</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16465; 33317</t>
+          <t>10788; 23022</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31589; 55878</t>
+          <t>29622; 50081</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>19796</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4800; 14931</t>
+          <t>5955; 16072</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6801; 17274</t>
+          <t>5100; 16982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13258; 28949</t>
+          <t>14075; 28567</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>63212</t>
+          <t>67870</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72948</t>
+          <t>59658</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136160</t>
+          <t>127528</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50049; 79068</t>
+          <t>54704; 82454</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58941; 87344</t>
+          <t>47929; 73762</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115365; 157366</t>
+          <t>110274; 145423</t>
         </is>
       </c>
     </row>
